--- a/산출물/1.데이터 수집 및 저장_WBS_ 1차_3TEAM.xlsx
+++ b/산출물/1.데이터 수집 및 저장_WBS_ 1차_3TEAM.xlsx
@@ -508,7 +508,7 @@
     <t>요약/확장 sLLM 파인튜닝 성능 평가</t>
   </si>
   <si>
-    <t>요약/확장 Stable-Diffusion 파인튜닝</t>
+    <t>요약/확장 MultiModal 파인튜닝</t>
   </si>
   <si>
     <t>우민규</t>
@@ -517,7 +517,7 @@
     <t>31일</t>
   </si>
   <si>
-    <t>요약/확장 Stable-Diffusion 파인튜닝 성능 평가</t>
+    <t>요약/확장 MultiModal 파인튜닝 성능 평가</t>
   </si>
   <si>
     <t>초안 작성 Process 설계</t>
@@ -1273,7 +1273,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1485,6 +1485,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -8848,7 +8851,7 @@
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
-      <c r="D80" s="69" t="s">
+      <c r="D80" s="100" t="s">
         <v>162</v>
       </c>
       <c r="E80" s="70" t="s">
@@ -8938,7 +8941,7 @@
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
-      <c r="D81" s="69" t="s">
+      <c r="D81" s="100" t="s">
         <v>165</v>
       </c>
       <c r="E81" s="70" t="s">
@@ -9695,7 +9698,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
-      <c r="AA89" s="100"/>
+      <c r="AA89" s="101"/>
       <c r="AB89" s="1"/>
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
@@ -9783,7 +9786,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
-      <c r="AA90" s="100"/>
+      <c r="AA90" s="101"/>
       <c r="AB90" s="1"/>
       <c r="AE90" s="1"/>
       <c r="AF90" s="97"/>
@@ -9871,7 +9874,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
-      <c r="AA91" s="100"/>
+      <c r="AA91" s="101"/>
       <c r="AB91" s="1"/>
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
@@ -9961,7 +9964,7 @@
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
-      <c r="AC92" s="100"/>
+      <c r="AC92" s="101"/>
       <c r="AD92" s="1"/>
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
@@ -10013,7 +10016,7 @@
       <c r="B93" s="59" t="s">
         <v>180</v>
       </c>
-      <c r="C93" s="101" t="s">
+      <c r="C93" s="102" t="s">
         <v>181</v>
       </c>
       <c r="D93" s="61"/>
@@ -10045,7 +10048,7 @@
       <c r="AD93" s="67"/>
       <c r="AE93" s="67"/>
       <c r="AF93" s="67"/>
-      <c r="AG93" s="102"/>
+      <c r="AG93" s="103"/>
       <c r="AH93" s="67"/>
       <c r="AI93" s="67"/>
       <c r="AJ93" s="67"/>
@@ -10275,7 +10278,7 @@
       <c r="D96" s="85" t="s">
         <v>184</v>
       </c>
-      <c r="E96" s="103" t="s">
+      <c r="E96" s="104" t="s">
         <v>53</v>
       </c>
       <c r="F96" s="70" t="s">
@@ -10284,13 +10287,13 @@
       <c r="G96" s="83">
         <v>1.0</v>
       </c>
-      <c r="H96" s="103" t="s">
+      <c r="H96" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I96" s="103" t="s">
+      <c r="I96" s="104" t="s">
         <v>104</v>
       </c>
-      <c r="J96" s="103" t="s">
+      <c r="J96" s="104" t="s">
         <v>56</v>
       </c>
       <c r="K96" s="84"/>
@@ -10360,7 +10363,7 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="104" t="s">
+      <c r="B97" s="105" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="75" t="s">
@@ -10394,8 +10397,8 @@
       <c r="AC97" s="82"/>
       <c r="AD97" s="82"/>
       <c r="AE97" s="82"/>
-      <c r="AF97" s="102"/>
-      <c r="AG97" s="102"/>
+      <c r="AF97" s="103"/>
+      <c r="AG97" s="103"/>
       <c r="AH97" s="67"/>
       <c r="AI97" s="1"/>
       <c r="AN97" s="82"/>
@@ -10678,14 +10681,14 @@
       <c r="BH100" s="93"/>
       <c r="BI100" s="74"/>
       <c r="BJ100" s="74"/>
-      <c r="BK100" s="105"/>
+      <c r="BK100" s="106"/>
       <c r="BL100" s="74"/>
       <c r="BM100" s="74"/>
       <c r="BN100" s="74"/>
       <c r="BP100" s="1"/>
-      <c r="BQ100" s="105"/>
+      <c r="BQ100" s="106"/>
       <c r="BR100" s="74"/>
-      <c r="BS100" s="105"/>
+      <c r="BS100" s="106"/>
       <c r="BT100" s="74"/>
       <c r="BU100" s="74"/>
       <c r="BV100" s="74"/>
@@ -10952,7 +10955,7 @@
       <c r="D104" s="85" t="s">
         <v>198</v>
       </c>
-      <c r="E104" s="103" t="s">
+      <c r="E104" s="104" t="s">
         <v>82</v>
       </c>
       <c r="F104" s="70" t="s">
@@ -10961,13 +10964,13 @@
       <c r="G104" s="83">
         <v>1.0</v>
       </c>
-      <c r="H104" s="103" t="s">
+      <c r="H104" s="104" t="s">
         <v>199</v>
       </c>
-      <c r="I104" s="103" t="s">
+      <c r="I104" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="J104" s="103" t="s">
+      <c r="J104" s="104" t="s">
         <v>59</v>
       </c>
       <c r="K104" s="84"/>
@@ -11002,7 +11005,7 @@
       <c r="AN104" s="87"/>
       <c r="AO104" s="87"/>
       <c r="AP104" s="87"/>
-      <c r="AQ104" s="106"/>
+      <c r="AQ104" s="107"/>
       <c r="AR104" s="84"/>
       <c r="AS104" s="84"/>
       <c r="AT104" s="84"/>
@@ -11026,7 +11029,7 @@
       <c r="BL104" s="88"/>
       <c r="BM104" s="88"/>
       <c r="BN104" s="88"/>
-      <c r="BO104" s="106"/>
+      <c r="BO104" s="107"/>
       <c r="BP104" s="84"/>
       <c r="BQ104" s="88"/>
       <c r="BR104" s="88"/>
@@ -11102,7 +11105,7 @@
       <c r="BK105" s="1"/>
       <c r="BL105" s="1"/>
       <c r="BM105" s="1"/>
-      <c r="BN105" s="107"/>
+      <c r="BN105" s="108"/>
       <c r="BO105" s="1"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -11119,10 +11122,10 @@
       <c r="G106" s="83">
         <v>1.0</v>
       </c>
-      <c r="H106" s="108" t="s">
+      <c r="H106" s="109" t="s">
         <v>113</v>
       </c>
-      <c r="I106" s="108" t="s">
+      <c r="I106" s="109" t="s">
         <v>19</v>
       </c>
       <c r="J106" s="90" t="s">
@@ -28735,375 +28738,375 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="110" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="110" t="str">
+      <c r="C1" s="111" t="str">
         <f>CONCATENATE(COUNTIF($A$4:$A$51,TRUE), "/", COUNTA($C$4:$C$51), " 완료됨  ")</f>
         <v>1/3 완료됨  </v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="111"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
     </row>
     <row r="3">
-      <c r="A3" s="112" t="s">
+      <c r="A3" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="B3" s="112" t="s">
+      <c r="B3" s="113" t="s">
         <v>204</v>
       </c>
-      <c r="C3" s="113" t="s">
+      <c r="C3" s="114" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="114" t="b">
+      <c r="A4" s="115" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="115">
+      <c r="B4" s="116">
         <v>36776.0</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="117" t="b">
+      <c r="A5" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B5" s="118">
+      <c r="B5" s="119">
         <v>36777.0</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="C5" s="120" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="117" t="b">
+      <c r="A6" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B6" s="118">
+      <c r="B6" s="119">
         <v>36778.0</v>
       </c>
-      <c r="C6" s="119" t="s">
+      <c r="C6" s="120" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="117" t="b">
+      <c r="A7" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B7" s="120"/>
-      <c r="C7" s="121"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="122"/>
     </row>
     <row r="8">
-      <c r="A8" s="117" t="b">
+      <c r="A8" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B8" s="120"/>
-      <c r="C8" s="121"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="122"/>
     </row>
     <row r="9">
-      <c r="A9" s="117" t="b">
+      <c r="A9" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B9" s="120"/>
-      <c r="C9" s="121"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="122"/>
     </row>
     <row r="10">
-      <c r="A10" s="117" t="b">
+      <c r="A10" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B10" s="120"/>
-      <c r="C10" s="121"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="122"/>
     </row>
     <row r="11">
-      <c r="A11" s="117" t="b">
+      <c r="A11" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B11" s="120"/>
-      <c r="C11" s="121"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="122"/>
     </row>
     <row r="12">
-      <c r="A12" s="117" t="b">
+      <c r="A12" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B12" s="120"/>
-      <c r="C12" s="121"/>
+      <c r="B12" s="121"/>
+      <c r="C12" s="122"/>
     </row>
     <row r="13">
-      <c r="A13" s="117" t="b">
+      <c r="A13" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B13" s="120"/>
-      <c r="C13" s="121"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="122"/>
     </row>
     <row r="14">
-      <c r="A14" s="117" t="b">
+      <c r="A14" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B14" s="120"/>
-      <c r="C14" s="121"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="122"/>
     </row>
     <row r="15">
-      <c r="A15" s="117" t="b">
+      <c r="A15" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B15" s="120"/>
-      <c r="C15" s="121"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="122"/>
     </row>
     <row r="16">
-      <c r="A16" s="117" t="b">
+      <c r="A16" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="121"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="122"/>
     </row>
     <row r="17">
-      <c r="A17" s="117" t="b">
+      <c r="A17" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B17" s="120"/>
-      <c r="C17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="122"/>
     </row>
     <row r="18">
-      <c r="A18" s="117" t="b">
+      <c r="A18" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B18" s="120"/>
-      <c r="C18" s="121"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="122"/>
     </row>
     <row r="19">
-      <c r="A19" s="117" t="b">
+      <c r="A19" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B19" s="120"/>
-      <c r="C19" s="121"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="122"/>
     </row>
     <row r="20">
-      <c r="A20" s="117" t="b">
+      <c r="A20" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B20" s="120"/>
-      <c r="C20" s="121"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="122"/>
     </row>
     <row r="21">
-      <c r="A21" s="117" t="b">
+      <c r="A21" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B21" s="120"/>
-      <c r="C21" s="121"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="122"/>
     </row>
     <row r="22">
-      <c r="A22" s="117" t="b">
+      <c r="A22" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B22" s="120"/>
-      <c r="C22" s="121"/>
+      <c r="B22" s="121"/>
+      <c r="C22" s="122"/>
     </row>
     <row r="23">
-      <c r="A23" s="117" t="b">
+      <c r="A23" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="121"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
     </row>
     <row r="24">
-      <c r="A24" s="117" t="b">
+      <c r="A24" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B24" s="120"/>
-      <c r="C24" s="121"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
     </row>
     <row r="25">
-      <c r="A25" s="117" t="b">
+      <c r="A25" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B25" s="120"/>
-      <c r="C25" s="121"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="122"/>
     </row>
     <row r="26">
-      <c r="A26" s="117" t="b">
+      <c r="A26" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B26" s="120"/>
-      <c r="C26" s="121"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
     </row>
     <row r="27">
-      <c r="A27" s="117" t="b">
+      <c r="A27" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B27" s="120"/>
-      <c r="C27" s="121"/>
+      <c r="B27" s="121"/>
+      <c r="C27" s="122"/>
     </row>
     <row r="28">
-      <c r="A28" s="117" t="b">
+      <c r="A28" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B28" s="120"/>
-      <c r="C28" s="121"/>
+      <c r="B28" s="121"/>
+      <c r="C28" s="122"/>
     </row>
     <row r="29">
-      <c r="A29" s="117" t="b">
+      <c r="A29" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B29" s="120"/>
-      <c r="C29" s="121"/>
+      <c r="B29" s="121"/>
+      <c r="C29" s="122"/>
     </row>
     <row r="30">
-      <c r="A30" s="117" t="b">
+      <c r="A30" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B30" s="120"/>
-      <c r="C30" s="121"/>
+      <c r="B30" s="121"/>
+      <c r="C30" s="122"/>
     </row>
     <row r="31">
-      <c r="A31" s="117" t="b">
+      <c r="A31" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B31" s="120"/>
-      <c r="C31" s="121"/>
+      <c r="B31" s="121"/>
+      <c r="C31" s="122"/>
     </row>
     <row r="32">
-      <c r="A32" s="117" t="b">
+      <c r="A32" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B32" s="120"/>
-      <c r="C32" s="121"/>
+      <c r="B32" s="121"/>
+      <c r="C32" s="122"/>
     </row>
     <row r="33">
-      <c r="A33" s="117" t="b">
+      <c r="A33" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B33" s="120"/>
-      <c r="C33" s="121"/>
+      <c r="B33" s="121"/>
+      <c r="C33" s="122"/>
     </row>
     <row r="34">
-      <c r="A34" s="117" t="b">
+      <c r="A34" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B34" s="120"/>
-      <c r="C34" s="121"/>
+      <c r="B34" s="121"/>
+      <c r="C34" s="122"/>
     </row>
     <row r="35">
-      <c r="A35" s="117" t="b">
+      <c r="A35" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B35" s="120"/>
-      <c r="C35" s="121"/>
+      <c r="B35" s="121"/>
+      <c r="C35" s="122"/>
     </row>
     <row r="36">
-      <c r="A36" s="117" t="b">
+      <c r="A36" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B36" s="120"/>
-      <c r="C36" s="121"/>
+      <c r="B36" s="121"/>
+      <c r="C36" s="122"/>
     </row>
     <row r="37">
-      <c r="A37" s="117" t="b">
+      <c r="A37" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B37" s="120"/>
-      <c r="C37" s="121"/>
+      <c r="B37" s="121"/>
+      <c r="C37" s="122"/>
     </row>
     <row r="38">
-      <c r="A38" s="117" t="b">
+      <c r="A38" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B38" s="120"/>
-      <c r="C38" s="121"/>
+      <c r="B38" s="121"/>
+      <c r="C38" s="122"/>
     </row>
     <row r="39">
-      <c r="A39" s="117" t="b">
+      <c r="A39" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B39" s="120"/>
-      <c r="C39" s="121"/>
+      <c r="B39" s="121"/>
+      <c r="C39" s="122"/>
     </row>
     <row r="40">
-      <c r="A40" s="117" t="b">
+      <c r="A40" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B40" s="120"/>
-      <c r="C40" s="121"/>
+      <c r="B40" s="121"/>
+      <c r="C40" s="122"/>
     </row>
     <row r="41">
-      <c r="A41" s="117" t="b">
+      <c r="A41" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B41" s="120"/>
-      <c r="C41" s="121"/>
+      <c r="B41" s="121"/>
+      <c r="C41" s="122"/>
     </row>
     <row r="42">
-      <c r="A42" s="117" t="b">
+      <c r="A42" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B42" s="120"/>
-      <c r="C42" s="121"/>
+      <c r="B42" s="121"/>
+      <c r="C42" s="122"/>
     </row>
     <row r="43">
-      <c r="A43" s="117" t="b">
+      <c r="A43" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B43" s="120"/>
-      <c r="C43" s="121"/>
+      <c r="B43" s="121"/>
+      <c r="C43" s="122"/>
     </row>
     <row r="44">
-      <c r="A44" s="117" t="b">
+      <c r="A44" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B44" s="120"/>
-      <c r="C44" s="121"/>
+      <c r="B44" s="121"/>
+      <c r="C44" s="122"/>
     </row>
     <row r="45">
-      <c r="A45" s="117" t="b">
+      <c r="A45" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B45" s="120"/>
-      <c r="C45" s="121"/>
+      <c r="B45" s="121"/>
+      <c r="C45" s="122"/>
     </row>
     <row r="46">
-      <c r="A46" s="117" t="b">
+      <c r="A46" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B46" s="120"/>
-      <c r="C46" s="121"/>
+      <c r="B46" s="121"/>
+      <c r="C46" s="122"/>
     </row>
     <row r="47">
-      <c r="A47" s="117" t="b">
+      <c r="A47" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B47" s="120"/>
-      <c r="C47" s="121"/>
+      <c r="B47" s="121"/>
+      <c r="C47" s="122"/>
     </row>
     <row r="48">
-      <c r="A48" s="117" t="b">
+      <c r="A48" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B48" s="120"/>
-      <c r="C48" s="121"/>
+      <c r="B48" s="121"/>
+      <c r="C48" s="122"/>
     </row>
     <row r="49">
-      <c r="A49" s="117" t="b">
+      <c r="A49" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B49" s="120"/>
-      <c r="C49" s="121"/>
+      <c r="B49" s="121"/>
+      <c r="C49" s="122"/>
     </row>
     <row r="50">
-      <c r="A50" s="117" t="b">
+      <c r="A50" s="118" t="b">
         <v>0</v>
       </c>
-      <c r="B50" s="120"/>
-      <c r="C50" s="121"/>
+      <c r="B50" s="121"/>
+      <c r="C50" s="122"/>
     </row>
     <row r="51">
-      <c r="A51" s="121"/>
-      <c r="B51" s="122"/>
-      <c r="C51" s="121"/>
+      <c r="A51" s="122"/>
+      <c r="B51" s="123"/>
+      <c r="C51" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -29127,26 +29130,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="124" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
     </row>
     <row r="2">
-      <c r="A2" s="124" t="s">
+      <c r="A2" s="125" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="125" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="124" t="s">
+      <c r="C2" s="125" t="s">
         <v>212</v>
       </c>
-      <c r="F2" s="124" t="s">
+      <c r="F2" s="125" t="s">
         <v>213</v>
       </c>
     </row>
@@ -29162,17 +29165,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="125">
+      <c r="A4" s="126">
         <v>45866.0</v>
       </c>
-      <c r="B4" s="126" t="s">
+      <c r="B4" s="127" t="s">
         <v>217</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="C4" s="127" t="s">
         <v>218</v>
       </c>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="1">
